--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484656_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484656_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9925</v>
+        <v>0.7375</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1834</v>
+        <v>2.7604</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1909</v>
+        <v>-2.0229</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2074</v>
+        <v>0.6044</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.036</v>
+        <v>-0.9952</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2434</v>
+        <v>1.5995</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6623</v>
+        <v>3.3033</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5789</v>
+        <v>1.3189</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0833</v>
+        <v>1.9845</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4549</v>
+        <v>-2.699</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6149</v>
+        <v>-2.314</v>
       </c>
       <c r="O3" t="n">
-        <v>0.16</v>
+        <v>-0.3849</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7406</v>
+        <v>0.3842</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9872</v>
+        <v>-0.543</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7534</v>
+        <v>0.9272</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9554</v>
+        <v>-1.9005</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5889</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6938</v>
+        <v>0.3251</v>
       </c>
       <c r="E4" t="n">
-        <v>2.568</v>
+        <v>0.3251</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8743</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6044</v>
+        <v>0.3251</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9952</v>
+        <v>0.3251</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5995</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3033</v>
+        <v>0.3251</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3189</v>
+        <v>0.3251</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9845</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.699</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.314</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3849</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3406</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7353</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0758</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5466</v>
+        <v>-0.2167</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6155</v>
+        <v>1.2219</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1621</v>
+        <v>-1.4386</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9139</v>
+        <v>0.2074</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6216</v>
+        <v>-0.036</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5355</v>
+        <v>0.2434</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3032</v>
+        <v>1.6623</v>
       </c>
       <c r="K5" t="n">
-        <v>3.418</v>
+        <v>1.5789</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.7211</v>
+        <v>0.0833</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6107</v>
+        <v>-1.4549</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.7964</v>
+        <v>-1.6149</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1857</v>
+        <v>0.16</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3823</v>
+        <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>2.251</v>
+        <v>0.5313</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2715</v>
+        <v>0.0257</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9794</v>
+        <v>0.5056</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2566</v>
+        <v>-0.9554</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3324</v>
+        <v>0.6335</v>
       </c>
       <c r="X5" t="n">
         <v>-1.5889</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>-0.2432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>-0.7117</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.4685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>-1.9139</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>0.6216</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-2.5355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>-0.3032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>3.418</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.7211</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.6107</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.7964</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.4612</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1754</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.2858</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2566</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7405</v>
+        <v>-0.7157</v>
       </c>
       <c r="E7" t="n">
         <v>-0.1235</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.617</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5918</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1486</v>
+        <v>-0.1239</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5915</v>
+        <v>-0.8135</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5438</v>
+        <v>2.0246</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1353</v>
+        <v>-2.8381</v>
       </c>
       <c r="G8" t="n">
         <v>1.6387</v>
@@ -1078,13 +1078,13 @@
         <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3531</v>
+        <v>0.425</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9004</v>
+        <v>-0.4196</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5473</v>
+        <v>0.8446</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3115</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7086</v>
+        <v>-1.3181</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9219</v>
+        <v>-1.7296</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2133</v>
+        <v>0.4115</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7451</v>
@@ -1156,13 +1156,13 @@
         <v>2.3823</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0526</v>
+        <v>0.3379</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6998</v>
+        <v>-0.5075</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6472</v>
+        <v>0.8454</v>
       </c>
       <c r="V9" t="n">
         <v>0.6231</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.866</v>
+        <v>-1.7451</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2768</v>
+        <v>-0.1806</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5892</v>
+        <v>-1.5644</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6623</v>
@@ -1234,13 +1234,13 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2037</v>
+        <v>-0.0828</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.842</v>
+        <v>-3.9463</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4188</v>
+        <v>-3.5726</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4233</v>
+        <v>-0.3737</v>
       </c>
       <c r="G11" t="n">
         <v>0.0245</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1756</v>
+        <v>1.0713</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8484</v>
+        <v>0.6946</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3271</v>
+        <v>0.3767</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6439</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7838</v>
+        <v>-4.9839</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1123</v>
+        <v>-4.5354</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6714</v>
+        <v>-0.4485</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6595</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9698</v>
+        <v>-0.1699</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8808</v>
+        <v>-0.3039</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5523</v>
+        <v>-6.7742</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7805</v>
+        <v>-3.2997</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7718</v>
+        <v>-3.4745</v>
       </c>
       <c r="G13" t="n">
         <v>-6.0084</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3606</v>
+        <v>-0.5826</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.046</v>
+        <v>-0.5652</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3146</v>
+        <v>-0.0174</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.684799999999999</v>
+        <v>-8.517300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.5317</v>
+        <v>-3.3394</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.1531</v>
+        <v>-5.1779</v>
       </c>
       <c r="G14" t="n">
         <v>-2.9768</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1479</v>
+        <v>0.3154</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1297</v>
+        <v>0.0626</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2776</v>
+        <v>0.2528</v>
       </c>
       <c r="V14" t="n">
         <v>-4.7563</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.9613</v>
+        <v>-26.9612</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.910499999999999</v>
+        <v>-9.910299999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.0509</v>
+        <v>-17.0508</v>
       </c>
       <c r="G15" t="n">
         <v>-15.5075</v>
@@ -1597,13 +1597,13 @@
         <v>-6.0906</v>
       </c>
       <c r="J15" t="n">
-        <v>5.902700000000001</v>
+        <v>5.902699999999999</v>
       </c>
       <c r="K15" t="n">
         <v>10.8687</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.9661</v>
+        <v>-4.966099999999999</v>
       </c>
       <c r="M15" t="n">
         <v>-21.4105</v>
@@ -1624,10 +1624,10 @@
         <v>13.7441</v>
       </c>
       <c r="S15" t="n">
-        <v>3.567299999999999</v>
+        <v>3.567099999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6703</v>
+        <v>-1.6702</v>
       </c>
       <c r="U15" t="n">
         <v>5.237299999999999</v>
@@ -1636,7 +1636,7 @@
         <v>-9.523</v>
       </c>
       <c r="W15" t="n">
-        <v>5.0991</v>
+        <v>5.099099999999999</v>
       </c>
       <c r="X15" t="n">
         <v>-14.6222</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.378</v>
+        <v>7.9628</v>
       </c>
       <c r="E16" t="n">
-        <v>6.904</v>
+        <v>6.7117</v>
       </c>
       <c r="F16" t="n">
-        <v>1.474</v>
+        <v>1.251</v>
       </c>
       <c r="G16" t="n">
         <v>4.004</v>
@@ -1702,13 +1702,13 @@
         <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4036</v>
+        <v>-0.8188</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5151</v>
+        <v>-0.7074</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1115</v>
+        <v>-0.1115</v>
       </c>
       <c r="V16" t="n">
         <v>2.212</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.502</v>
+        <v>5.5834</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8496</v>
+        <v>4.4265</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6524</v>
+        <v>1.157</v>
       </c>
       <c r="G17" t="n">
         <v>3.0912</v>
@@ -1780,13 +1780,13 @@
         <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4555</v>
+        <v>-0.3741</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2111</v>
+        <v>-0.6342</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7556</v>
+        <v>0.2601</v>
       </c>
       <c r="V17" t="n">
         <v>2.8663</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.8173</v>
+        <v>4.9878</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0306</v>
+        <v>2.1268</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7867</v>
+        <v>2.8611</v>
       </c>
       <c r="G18" t="n">
         <v>0.2304</v>
@@ -1858,13 +1858,13 @@
         <v>3.6651</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0674</v>
+        <v>-0.8969</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1206</v>
+        <v>-1.0245</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0533</v>
+        <v>0.1276</v>
       </c>
       <c r="V18" t="n">
         <v>3.8217</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. PALAU LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8192</v>
+        <v>2.1754</v>
       </c>
       <c r="E20" t="n">
-        <v>2.544</v>
+        <v>1.9004</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2753</v>
+        <v>0.275</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5975</v>
+        <v>0.6563</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9537</v>
+        <v>0.2781</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5512</v>
+        <v>0.3783</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3321</v>
+        <v>0.6885</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5819</v>
+        <v>0.0217</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7501</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7345</v>
+        <v>-0.0321</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5356</v>
+        <v>0.2564</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8011</v>
+        <v>-0.2885</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2663</v>
+        <v>0.0688</v>
       </c>
       <c r="T20" t="n">
-        <v>0.822</v>
+        <v>-0.0551</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4442</v>
+        <v>0.1239</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2224</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PALAU LOPEZ</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1011</v>
+        <v>1.8447</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9004</v>
+        <v>0.0576</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2007</v>
+        <v>1.7872</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6563</v>
+        <v>2.6274</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2781</v>
+        <v>1.6593</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3783</v>
+        <v>0.9681</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6885</v>
+        <v>3.0734</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0217</v>
+        <v>2.2975</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.7759</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0321</v>
+        <v>-0.446</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2564</v>
+        <v>-0.6382</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2885</v>
+        <v>0.1922</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1833</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0055</v>
+        <v>-0.0496</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0551</v>
+        <v>-0.267</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0495</v>
+        <v>0.2174</v>
       </c>
       <c r="V21" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8636</v>
+        <v>1.3929</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2499</v>
+        <v>1.3901</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6138</v>
+        <v>0.0028</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6274</v>
+        <v>0.5975</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6593</v>
+        <v>-0.9537</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9681</v>
+        <v>1.5512</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0734</v>
+        <v>1.3321</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2975</v>
+        <v>0.5819</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7759</v>
+        <v>0.7501</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.446</v>
+        <v>-0.7345</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6382</v>
+        <v>-1.5356</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1922</v>
+        <v>0.8011</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.733</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0307</v>
+        <v>-0.1601</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0746</v>
+        <v>-0.3318</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0439</v>
+        <v>0.1717</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. FAS MONROS</t>
+          <t>I. RUIPEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7412</v>
+        <v>0.8811</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0694</v>
+        <v>0.3576</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6718</v>
+        <v>0.5235</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5326</v>
+        <v>0.3161</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7699</v>
+        <v>-1.1491</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2373</v>
+        <v>1.4653</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7739</v>
+        <v>1.9009</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6906</v>
+        <v>0.5635</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0833</v>
+        <v>1.3374</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2413</v>
+        <v>-1.5848</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0793</v>
+        <v>-1.7127</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3207</v>
+        <v>0.1279</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0149</v>
+        <v>-0.5633</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1652</v>
+        <v>-0.9777</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1801</v>
+        <v>0.4144</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6231</v>
+        <v>0.945</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6231</v>
+        <v>1.267</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>R. FAS MONROS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6502</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6502</v>
+        <v>0.0694</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6502</v>
+        <v>1.5326</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6502</v>
+        <v>1.7699</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-0.2373</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6502</v>
+        <v>1.7739</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6502</v>
+        <v>1.6906</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>-0.2413</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.0793</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>-0.3207</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.0645</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-0.1652</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.2296</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. RUIPEREZ SANCHEZ</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.543</v>
+        <v>0.6502</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.6502</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4739</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3161</v>
+        <v>0.6502</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1491</v>
+        <v>0.6502</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4653</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9009</v>
+        <v>0.6502</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5635</v>
+        <v>0.6502</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3374</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5848</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7127</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1279</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9014</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2662</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6642</v>
+        <v>-0.2926</v>
       </c>
       <c r="E26" t="n">
         <v>-0.8939</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2296</v>
+        <v>0.6012</v>
       </c>
       <c r="G26" t="n">
         <v>1.0802</v>
@@ -2482,13 +2482,13 @@
         <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0901</v>
+        <v>-0.7185</v>
       </c>
       <c r="T26" t="n">
         <v>-0.7157</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3744</v>
+        <v>-0.0028</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6543</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.6661</v>
+        <v>-1.891</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.1982</v>
+        <v>-2.6213</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5321</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-2.1542</v>
@@ -2560,13 +2560,13 @@
         <v>1.6493</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8943</v>
+        <v>-0.1192</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9359</v>
+        <v>-0.359</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0416</v>
+        <v>0.2398</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>26.9611</v>
+        <v>26.9613</v>
       </c>
       <c r="E28" t="n">
         <v>17.0509</v>
       </c>
       <c r="F28" t="n">
-        <v>9.910299999999999</v>
+        <v>9.910399999999999</v>
       </c>
       <c r="G28" t="n">
         <v>15.5075</v>
@@ -2608,7 +2608,7 @@
         <v>9.416899999999998</v>
       </c>
       <c r="I28" t="n">
-        <v>6.0907</v>
+        <v>6.090699999999999</v>
       </c>
       <c r="J28" t="n">
         <v>21.4104</v>
@@ -2620,7 +2620,7 @@
         <v>1.1243</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.9027</v>
+        <v>-5.902699999999999</v>
       </c>
       <c r="N28" t="n">
         <v>-10.8689</v>
@@ -2629,7 +2629,7 @@
         <v>4.9663</v>
       </c>
       <c r="P28" t="n">
-        <v>5.4978</v>
+        <v>5.497800000000001</v>
       </c>
       <c r="Q28" t="n">
         <v>-13.7445</v>
@@ -2638,16 +2638,16 @@
         <v>19.242</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.5673</v>
+        <v>-3.5672</v>
       </c>
       <c r="T28" t="n">
-        <v>-5.237500000000001</v>
+        <v>-5.2376</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6701</v>
+        <v>1.6702</v>
       </c>
       <c r="V28" t="n">
-        <v>9.523000000000001</v>
+        <v>9.523</v>
       </c>
       <c r="W28" t="n">
         <v>14.6222</v>
